--- a/data_generation/10_aquatic_toxicity/indoxacarb_aquatic_toxicity.xlsx
+++ b/data_generation/10_aquatic_toxicity/indoxacarb_aquatic_toxicity.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Data-Work\41_AssessmentPPP-RE\412.34_Projekte\054_derappp\05_Daten\Input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Data-Work\41_AssessmentPPP-RE\412.34_Projekte\054_derappp\05_Daten\Input\10_aquatic_toxicity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C808A41-CD84-4741-911F-42DDA705CE41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD73CAE-9B9A-4649-811F-35B55226E509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15" yWindow="2730" windowWidth="28785" windowHeight="8790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="aquatic_endpoints" sheetId="6" r:id="rId1"/>
@@ -150,9 +150,6 @@
     <t>Mysidopsis bahia</t>
   </si>
   <si>
-    <t>ini</t>
-  </si>
-  <si>
     <t>21 d</t>
   </si>
   <si>
@@ -250,6 +247,9 @@
   </si>
   <si>
     <t>early life stage</t>
+  </si>
+  <si>
+    <t>im</t>
   </si>
 </sst>
 </file>
@@ -609,7 +609,7 @@
   <sheetData>
     <row r="1" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>5</v>
@@ -618,31 +618,31 @@
         <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>10</v>
@@ -669,15 +669,15 @@
         <v>19</v>
       </c>
       <c r="U1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
@@ -711,7 +711,7 @@
         <v>4</v>
       </c>
       <c r="P2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q2">
         <v>103</v>
@@ -724,15 +724,15 @@
       </c>
       <c r="T2" s="2"/>
       <c r="U2" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>26</v>
@@ -765,7 +765,7 @@
         <v>4</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q3" s="2">
         <v>103</v>
@@ -777,21 +777,21 @@
         <v>18</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>22</v>
@@ -821,7 +821,7 @@
         <v>29</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q4" s="2">
         <v>103</v>
@@ -834,15 +834,15 @@
       </c>
       <c r="T4" s="2"/>
       <c r="U4" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
@@ -858,7 +858,7 @@
         <v>31</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K5" t="s">
         <v>32</v>
@@ -873,7 +873,7 @@
         <v>4</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q5" s="2">
         <v>103</v>
@@ -885,18 +885,18 @@
         <v>18</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>26</v>
@@ -914,7 +914,7 @@
         <v>33</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K6" t="s">
         <v>32</v>
@@ -929,7 +929,7 @@
         <v>4</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q6" s="2">
         <v>103</v>
@@ -941,18 +941,18 @@
         <v>18</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
@@ -986,7 +986,7 @@
         <v>4</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q7" s="2">
         <v>104</v>
@@ -999,15 +999,15 @@
       </c>
       <c r="T7" s="2"/>
       <c r="U7" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
@@ -1041,7 +1041,7 @@
         <v>4</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q8" s="2">
         <v>104</v>
@@ -1054,18 +1054,18 @@
       </c>
       <c r="T8" s="2"/>
       <c r="U8" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>1</v>
@@ -1092,10 +1092,10 @@
         <v>15</v>
       </c>
       <c r="O9" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q9" s="2">
         <v>104</v>
@@ -1107,21 +1107,21 @@
         <v>18</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>36</v>
@@ -1148,10 +1148,10 @@
         <v>15</v>
       </c>
       <c r="O10" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q10" s="2">
         <v>104</v>
@@ -1164,15 +1164,15 @@
       </c>
       <c r="T10" s="2"/>
       <c r="U10" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
@@ -1185,13 +1185,13 @@
         <v>35</v>
       </c>
       <c r="G11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" t="s">
+        <v>68</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="I11" t="s">
-        <v>69</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="K11" t="s">
         <v>32</v>
@@ -1206,7 +1206,7 @@
         <v>4</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q11" s="2">
         <v>104</v>
@@ -1219,15 +1219,15 @@
       </c>
       <c r="T11" s="2"/>
       <c r="U11" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>26</v>
@@ -1245,10 +1245,10 @@
         <v>31</v>
       </c>
       <c r="I12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K12" t="s">
         <v>32</v>
@@ -1263,7 +1263,7 @@
         <v>4</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q12" s="2">
         <v>104</v>
@@ -1275,18 +1275,18 @@
         <v>18</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
@@ -1302,10 +1302,10 @@
         <v>31</v>
       </c>
       <c r="I13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K13" t="s">
         <v>32</v>
@@ -1320,7 +1320,7 @@
         <v>4</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q13" s="2">
         <v>104</v>
@@ -1333,19 +1333,19 @@
       </c>
       <c r="T13" s="2"/>
       <c r="U13" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D14" s="2">
         <v>13</v>
@@ -1370,7 +1370,7 @@
         <v>4</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q14" s="2">
         <v>105</v>
@@ -1382,22 +1382,22 @@
         <v>18</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D15" s="2">
         <v>14</v>
@@ -1409,10 +1409,10 @@
         <v>31</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K15" t="s">
         <v>32</v>
@@ -1427,7 +1427,7 @@
         <v>4</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q15" s="2">
         <v>105</v>
@@ -1439,22 +1439,22 @@
         <v>18</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V15" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D16" s="2">
         <v>16</v>
@@ -1463,10 +1463,10 @@
         <v>28</v>
       </c>
       <c r="G16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="K16" t="s">
         <v>2</v>
@@ -1484,7 +1484,7 @@
         <v>4</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q16" s="2">
         <v>106</v>
@@ -1497,19 +1497,19 @@
       </c>
       <c r="T16" s="2"/>
       <c r="U16" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D17" s="2">
         <v>16</v>
@@ -1518,10 +1518,10 @@
         <v>28</v>
       </c>
       <c r="G17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="K17" t="s">
         <v>32</v>
@@ -1536,7 +1536,7 @@
         <v>4</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q17" s="2">
         <v>106</v>
@@ -1549,19 +1549,19 @@
       </c>
       <c r="T17" s="2"/>
       <c r="U17" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V17" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D18" s="2">
         <v>16</v>
@@ -1570,10 +1570,10 @@
         <v>28</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>2</v>
@@ -1591,7 +1591,7 @@
         <v>4</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q18" s="2">
         <v>106</v>
@@ -1604,19 +1604,19 @@
       </c>
       <c r="T18" s="2"/>
       <c r="U18" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D19" s="2">
         <v>16</v>
@@ -1625,10 +1625,10 @@
         <v>28</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>32</v>
@@ -1643,7 +1643,7 @@
         <v>4</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q19" s="2">
         <v>106</v>
@@ -1656,19 +1656,19 @@
       </c>
       <c r="T19" s="2"/>
       <c r="U19" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V19" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D20" s="2">
         <v>16</v>
@@ -1677,10 +1677,10 @@
         <v>28</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>2</v>
@@ -1698,7 +1698,7 @@
         <v>4</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q20" s="2">
         <v>106</v>
@@ -1711,19 +1711,19 @@
       </c>
       <c r="T20" s="2"/>
       <c r="U20" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V20" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D21" s="2">
         <v>16</v>
@@ -1732,10 +1732,10 @@
         <v>28</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>32</v>
@@ -1750,7 +1750,7 @@
         <v>4</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q21" s="2">
         <v>106</v>
@@ -1763,21 +1763,21 @@
       </c>
       <c r="T21" s="2"/>
       <c r="U21" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V21" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D22" s="2">
         <v>17</v>
@@ -1786,10 +1786,10 @@
         <v>28</v>
       </c>
       <c r="G22" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>2</v>
@@ -1807,7 +1807,7 @@
         <v>29</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q22" s="2">
         <v>106</v>
@@ -1820,21 +1820,21 @@
       </c>
       <c r="T22" s="2"/>
       <c r="U22" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V22" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D23" s="2">
         <v>17</v>
@@ -1843,10 +1843,10 @@
         <v>28</v>
       </c>
       <c r="G23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>32</v>
@@ -1861,7 +1861,7 @@
         <v>29</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q23" s="2">
         <v>106</v>
@@ -1874,21 +1874,21 @@
       </c>
       <c r="T23" s="2"/>
       <c r="U23" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V23" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D24" s="2">
         <v>17</v>
@@ -1897,10 +1897,10 @@
         <v>28</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>2</v>
@@ -1915,7 +1915,7 @@
         <v>29</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q24" s="2">
         <v>106</v>
@@ -1928,21 +1928,21 @@
       </c>
       <c r="T24" s="2"/>
       <c r="U24" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V24" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D25" s="2">
         <v>17</v>
@@ -1951,10 +1951,10 @@
         <v>28</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>32</v>
@@ -1969,7 +1969,7 @@
         <v>29</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q25" s="2">
         <v>106</v>
@@ -1982,10 +1982,10 @@
       </c>
       <c r="T25" s="2"/>
       <c r="U25" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V25" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
